--- a/grupos/3BEM - Estadisticos 20231.xlsx
+++ b/grupos/3BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -188,24 +188,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
+    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,139 +218,91 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>PALOMINO</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>ACOSTA</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>SALOMON</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
     <t>MIGUEL ANTONIO</t>
   </si>
   <si>
-    <t>AARON MIGUEL</t>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
   </si>
   <si>
     <t>JULIAN DAVID</t>
   </si>
   <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
-    <t>FEDERICO ABIMAEL</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>BELEN</t>
-  </si>
-  <si>
     <t>ABIEL NEFTALI</t>
   </si>
   <si>
-    <t>ARLETT</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>GEOVANNI</t>
@@ -864,19 +816,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -900,16 +852,16 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -941,19 +893,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -977,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -986,7 +938,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1018,19 +970,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1054,16 +1006,16 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>9</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1095,19 +1047,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1131,19 +1083,19 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1172,19 +1124,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1249,19 +1201,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1285,19 +1237,19 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1326,19 +1278,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1362,13 +1314,13 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1403,19 +1355,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1439,19 +1391,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1480,19 +1432,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1516,16 +1468,16 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1557,19 +1509,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1593,16 +1545,16 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1634,19 +1586,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1670,10 +1622,10 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1682,7 +1634,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1711,19 +1663,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1747,16 +1699,16 @@
         <v>7</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1788,19 +1740,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1824,16 +1776,16 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1865,19 +1817,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1901,7 +1853,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1913,7 +1865,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1942,19 +1894,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1978,19 +1930,19 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2019,19 +1971,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2055,16 +2007,16 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2096,19 +2048,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2135,13 +2087,13 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2173,19 +2125,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2209,16 +2161,16 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2250,19 +2202,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2286,16 +2238,16 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2327,19 +2279,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2363,19 +2315,19 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2404,19 +2356,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2440,19 +2392,19 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>9</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2481,19 +2433,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2517,16 +2469,16 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2558,19 +2510,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2594,16 +2546,16 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2635,19 +2587,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2671,10 +2623,10 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2712,19 +2664,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2748,16 +2700,16 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2789,19 +2741,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2825,19 +2777,19 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2866,19 +2818,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2902,16 +2854,16 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -2943,19 +2895,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2979,16 +2931,16 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3020,19 +2972,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3056,19 +3008,19 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3097,19 +3049,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3133,10 +3085,10 @@
         <v>8</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3174,19 +3126,19 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3210,16 +3162,16 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>9</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3251,19 +3203,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3287,10 +3239,10 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3556,7 +3508,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3574,7 +3526,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3615,7 +3567,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3633,7 +3585,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3733,7 +3685,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3751,7 +3703,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3792,7 +3744,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3801,7 +3753,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M10">
         <v>90</v>
@@ -3810,7 +3762,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3819,7 +3771,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S10">
         <v>90</v>
@@ -3851,7 +3803,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3860,17 +3812,17 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M11">
+        <v>92.5</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
         <v>95</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>90</v>
-      </c>
       <c r="P11">
         <v>100</v>
       </c>
@@ -3878,10 +3830,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S11">
-        <v>95</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3910,7 +3862,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3922,13 +3874,13 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N12">
         <v>100</v>
       </c>
       <c r="O12">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -3940,7 +3892,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3969,7 +3921,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -3981,13 +3933,13 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3999,7 +3951,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4037,7 +3989,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -4055,7 +4007,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4087,7 +4039,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4105,7 +4057,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4273,7 +4225,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -4291,7 +4243,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4323,37 +4275,37 @@
         <v>100</v>
       </c>
       <c r="I19">
+        <v>97.5</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
+        <v>93.3</v>
+      </c>
+      <c r="M19">
         <v>95</v>
       </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
-        <v>90</v>
-      </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
+        <v>97.5</v>
+      </c>
+      <c r="P19">
+        <v>100</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>93.3</v>
+      </c>
+      <c r="S19">
         <v>95</v>
-      </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
-        <v>100</v>
-      </c>
-      <c r="S19">
-        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4441,16 +4393,16 @@
         <v>75</v>
       </c>
       <c r="I21">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>76</v>
+        <v>68.8</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>56.7</v>
       </c>
       <c r="M21">
         <v>80</v>
@@ -4459,16 +4411,16 @@
         <v>75</v>
       </c>
       <c r="O21">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>76</v>
+        <v>68.8</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>56.7</v>
       </c>
       <c r="S21">
         <v>80</v>
@@ -4568,10 +4520,10 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4586,10 +4538,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4630,7 +4582,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -4648,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4677,7 +4629,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -4695,7 +4647,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4736,7 +4688,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4745,7 +4697,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -4754,7 +4706,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4763,7 +4715,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4804,7 +4756,7 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -4822,7 +4774,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -4863,7 +4815,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -4881,7 +4833,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>58.3</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -4922,10 +4874,10 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M29">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -4940,10 +4892,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S29">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5031,7 +4983,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J31">
         <v>100</v>
@@ -5049,7 +5001,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5102,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -5120,7 +5072,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5149,7 +5101,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5158,7 +5110,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -5167,7 +5119,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5176,7 +5128,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5276,7 +5228,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -5294,7 +5246,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -5354,7 +5306,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5363,19 +5315,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>59.4</v>
+        <v>68.8</v>
       </c>
       <c r="G2" s="2">
-        <v>40.6</v>
+        <v>31.2</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5386,7 +5338,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5395,19 +5347,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>68.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>31.2</v>
+        <v>9.4</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5418,7 +5370,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5427,19 +5379,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>78.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="G4" s="2">
-        <v>21.9</v>
+        <v>6.2</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5450,7 +5402,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5459,19 +5411,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>90.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5482,7 +5434,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -5503,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5514,7 +5466,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -5535,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5585,7 +5537,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5617,22 +5569,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920038</v>
+        <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5640,22 +5592,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920038</v>
+        <v>22330051920034</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5663,22 +5615,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920043</v>
+        <v>22330051920189</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5686,22 +5638,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920043</v>
+        <v>22330051920189</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5709,22 +5661,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920045</v>
+        <v>22330051920043</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5732,22 +5684,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920045</v>
+        <v>22330051920043</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5755,19 +5707,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920035</v>
+        <v>22330051920038</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
@@ -5778,19 +5730,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920036</v>
+        <v>22330051920039</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -5801,19 +5753,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920037</v>
+        <v>22330051920191</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
@@ -5824,19 +5776,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920331</v>
+        <v>22330051920045</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>56</v>
@@ -5847,22 +5799,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920039</v>
+        <v>22330051920047</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5870,22 +5822,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920191</v>
+        <v>22330051920049</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5893,162 +5845,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920327</v>
+        <v>22330051920051</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920141</v>
-      </c>
-      <c r="B15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920047</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920198</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920329</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920203</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920051</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20231.xlsx
+++ b/grupos/3BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -227,9 +227,6 @@
     <t>PALOMINO</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -245,9 +242,6 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -257,9 +251,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
@@ -275,9 +266,6 @@
     <t>SALOMON</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
@@ -287,9 +275,6 @@
     <t>AARON MIGUEL</t>
   </si>
   <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
     <t>ROGGER JUSEFH</t>
   </si>
   <si>
@@ -303,9 +288,6 @@
   </si>
   <si>
     <t>DANIEL</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
   </si>
 </sst>
 </file>
@@ -813,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -849,7 +831,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>8</v>
@@ -890,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>9</v>
@@ -926,7 +908,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -967,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -1003,7 +985,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1044,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1121,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>9</v>
@@ -1198,7 +1180,7 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -1234,7 +1216,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1275,7 +1257,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>9</v>
@@ -1352,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>9</v>
@@ -1429,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1506,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1542,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1583,7 +1565,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -1619,7 +1601,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1660,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1737,7 +1719,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>9</v>
@@ -1773,7 +1755,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>7</v>
@@ -1814,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>9</v>
@@ -1891,7 +1873,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>9</v>
@@ -1968,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -2045,7 +2027,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>9</v>
@@ -2081,7 +2063,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2122,7 +2104,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2199,7 +2181,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -2235,7 +2217,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2276,7 +2258,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2312,7 +2294,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2353,7 +2335,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>9</v>
@@ -2389,7 +2371,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>8</v>
@@ -2430,7 +2412,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2507,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -2543,7 +2525,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2584,7 +2566,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -2661,7 +2643,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -2738,7 +2720,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -2815,7 +2797,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>9</v>
@@ -2851,7 +2833,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -2892,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -2928,7 +2910,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -2969,7 +2951,7 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -3046,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3123,7 +3105,7 @@
         <v>10</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>9</v>
@@ -3200,7 +3182,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
         <v>9</v>
@@ -3236,7 +3218,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -4390,7 +4372,7 @@
         <v>80</v>
       </c>
       <c r="H21">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="I21">
         <v>92.5</v>
@@ -4408,7 +4390,7 @@
         <v>80</v>
       </c>
       <c r="N21">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="O21">
         <v>92.5</v>
@@ -5315,19 +5297,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5537,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5575,10 +5557,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5598,10 +5580,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5621,10 +5603,10 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5644,10 +5626,10 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5667,10 +5649,10 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5690,10 +5672,10 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5707,16 +5689,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920038</v>
+        <v>22330051920039</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5730,16 +5712,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920039</v>
+        <v>22330051920191</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -5753,16 +5735,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920191</v>
+        <v>22330051920045</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5776,16 +5758,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920045</v>
+        <v>22330051920047</v>
       </c>
       <c r="B11" t="s">
         <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -5799,16 +5781,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920047</v>
+        <v>22330051920049</v>
       </c>
       <c r="B12" t="s">
         <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -5817,52 +5799,6 @@
         <v>56</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920049</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920051</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20231.xlsx
+++ b/grupos/3BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -230,18 +230,12 @@
     <t>LUNA</t>
   </si>
   <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -254,18 +248,12 @@
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
@@ -278,16 +266,10 @@
     <t>ROGGER JUSEFH</t>
   </si>
   <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
     <t>JULIAN DAVID</t>
   </si>
   <si>
     <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
   </si>
 </sst>
 </file>
@@ -1950,7 +1932,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -1986,7 +1968,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2951,7 +2933,7 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -2987,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -4679,7 +4661,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -4697,7 +4679,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4797,7 +4779,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -4815,7 +4797,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>58.3</v>
+        <v>100</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5297,19 +5279,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5519,7 +5501,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5557,10 +5539,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5580,10 +5562,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5603,10 +5585,10 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5626,10 +5608,10 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -5649,10 +5631,10 @@
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5672,10 +5654,10 @@
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5695,10 +5677,10 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5712,16 +5694,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920191</v>
+        <v>22330051920045</v>
       </c>
       <c r="B9" t="s">
         <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -5735,16 +5717,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920045</v>
+        <v>22330051920047</v>
       </c>
       <c r="B10" t="s">
         <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5753,52 +5735,6 @@
         <v>56</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920047</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920049</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20231.xlsx
+++ b/grupos/3BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -194,18 +194,18 @@
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,52 +224,25 @@
     <t>JENKINS</t>
   </si>
   <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
     <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
   </si>
 </sst>
 </file>
@@ -795,34 +768,34 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>8</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -872,22 +845,22 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -949,22 +922,22 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -973,7 +946,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -982,7 +955,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1026,22 +999,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1050,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1103,22 +1076,22 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1180,22 +1153,22 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1204,7 +1177,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1257,22 +1230,22 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1290,7 +1263,7 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1334,22 +1307,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1367,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1411,22 +1384,22 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1488,34 +1461,34 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1565,28 +1538,28 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1595,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1642,37 +1615,37 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>7</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1719,22 +1692,22 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1743,13 +1716,13 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1796,22 +1769,22 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1820,16 +1793,16 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1873,22 +1846,22 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -1897,13 +1870,13 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -1950,28 +1923,28 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -1980,7 +1953,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2027,22 +2000,22 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2104,22 +2077,22 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2128,10 +2101,10 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2181,25 +2154,25 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2258,40 +2231,40 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2335,22 +2308,22 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2412,28 +2385,28 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2489,28 +2462,28 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2566,31 +2539,31 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2643,22 +2616,22 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2667,10 +2640,10 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2720,28 +2693,28 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>8</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2753,7 +2726,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2797,22 +2770,22 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -2874,22 +2847,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>8</v>
@@ -2951,25 +2924,25 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -2981,10 +2954,10 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3028,22 +3001,22 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3105,28 +3078,28 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>9</v>
@@ -3182,31 +3155,31 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3490,7 +3463,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3499,7 +3472,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3549,7 +3522,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3667,7 +3640,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3726,7 +3699,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -3735,10 +3708,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>96.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S10">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3785,7 +3758,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3794,10 +3767,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>98.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S11">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3844,7 +3817,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -3856,7 +3829,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3903,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3912,10 +3885,10 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="S13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3971,7 +3944,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>96.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4021,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4080,7 +4053,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -4207,7 +4180,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>93.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4257,7 +4230,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4266,10 +4239,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>93.3</v>
+        <v>92.2</v>
       </c>
       <c r="S19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4372,22 +4345,22 @@
         <v>80</v>
       </c>
       <c r="N21">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="O21">
-        <v>92.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>68.8</v>
+        <v>56.2</v>
       </c>
       <c r="R21">
-        <v>56.7</v>
+        <v>40</v>
       </c>
       <c r="S21">
-        <v>80</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4434,7 +4407,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4502,10 +4475,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="S23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4564,7 +4537,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4611,7 +4584,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4620,7 +4593,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4670,7 +4643,7 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4738,7 +4711,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -4847,7 +4820,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -4856,10 +4829,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="S29">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4965,7 +4938,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5024,7 +4997,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -5033,10 +5006,10 @@
         <v>100</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S32">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5065,7 +5038,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5083,7 +5056,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>50</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P33">
         <v>100</v>
@@ -5092,7 +5065,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5151,7 +5124,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -5210,7 +5183,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>96.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -5279,19 +5252,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>81.2</v>
+        <v>87.5</v>
       </c>
       <c r="G2" s="2">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5311,16 +5284,16 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>90.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="H3">
         <v>8.300000000000001</v>
@@ -5334,7 +5307,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5343,19 +5316,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5387,7 +5360,7 @@
         <v>3.1</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5419,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5430,7 +5403,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -5451,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5501,7 +5474,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5539,10 +5512,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
         <v>72</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5556,22 +5529,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920034</v>
+        <v>22330051920189</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5579,16 +5552,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920189</v>
+        <v>22330051920039</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5597,144 +5570,6 @@
         <v>56</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920189</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920043</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920043</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920039</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920045</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920047</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20231.xlsx
+++ b/grupos/3BEM - Estadisticos 20231.xlsx
@@ -786,22 +786,22 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -863,22 +863,22 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -940,22 +940,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1020,16 +1020,16 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1094,10 +1094,10 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1171,22 +1171,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1251,19 +1251,19 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1328,19 +1328,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1402,22 +1402,22 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1479,22 +1479,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1556,22 +1556,22 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1633,22 +1633,22 @@
         <v>8</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1710,22 +1710,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1790,19 +1790,19 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1867,19 +1867,19 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1941,22 +1941,22 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2018,22 +2018,22 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2098,10 +2098,10 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2172,22 +2172,22 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2249,22 +2249,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2326,22 +2326,22 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2403,22 +2403,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2480,19 +2480,19 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2557,22 +2557,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2634,22 +2634,22 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2711,22 +2711,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2788,13 +2788,13 @@
         <v>9</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -2803,7 +2803,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2865,13 +2865,13 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -2942,22 +2942,22 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3019,19 +3019,19 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3096,19 +3096,19 @@
         <v>10</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3173,22 +3173,22 @@
         <v>9</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5264,7 +5264,7 @@
         <v>12.5</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5296,7 +5296,7 @@
         <v>3.1</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>3.1</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>3.1</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3BEM - Estadisticos 20231.xlsx
+++ b/grupos/3BEM - Estadisticos 20231.xlsx
@@ -786,22 +786,22 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -863,22 +863,22 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>10</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -940,22 +940,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1020,16 +1020,16 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1094,10 +1094,10 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1171,22 +1171,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1251,19 +1251,19 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1328,19 +1328,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1402,22 +1402,22 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1479,22 +1479,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1556,22 +1556,22 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1633,22 +1633,22 @@
         <v>8</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1710,22 +1710,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1790,19 +1790,19 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1867,19 +1867,19 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1941,22 +1941,22 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2018,22 +2018,22 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2098,10 +2098,10 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2172,22 +2172,22 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2249,22 +2249,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2326,22 +2326,22 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2403,22 +2403,22 @@
         <v>8</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2480,19 +2480,19 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>10</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2557,22 +2557,22 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2634,22 +2634,22 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2711,22 +2711,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2788,13 +2788,13 @@
         <v>9</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -2803,7 +2803,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2865,13 +2865,13 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -2942,22 +2942,22 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3019,19 +3019,19 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3096,19 +3096,19 @@
         <v>10</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3173,22 +3173,22 @@
         <v>9</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5264,7 +5264,7 @@
         <v>12.5</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5296,7 +5296,7 @@
         <v>3.1</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>3.1</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>3.1</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
